--- a/data/trans_dic/P16A08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,18</t>
+          <t>2,03; 5,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,33</t>
+          <t>2,46; 6,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,44</t>
+          <t>2,33; 6,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,24</t>
+          <t>1,78; 9,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,63</t>
+          <t>2,4; 5,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,29</t>
+          <t>4,47; 9,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,26</t>
+          <t>3,52; 8,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,16</t>
+          <t>1,49; 7,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,97</t>
+          <t>2,58; 4,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,7</t>
+          <t>3,86; 6,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,42</t>
+          <t>3,38; 6,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,73</t>
+          <t>2,01; 6,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,14</t>
+          <t>1,45; 4,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,84</t>
+          <t>2,56; 5,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,38</t>
+          <t>2,28; 5,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,63</t>
+          <t>3,15; 9,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,21</t>
+          <t>2,73; 6,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,26</t>
+          <t>4,36; 8,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,36</t>
+          <t>4,3; 8,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 50,7</t>
+          <t>5,82; 52,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,37</t>
+          <t>2,35; 4,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,36</t>
+          <t>3,98; 6,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,12</t>
+          <t>3,72; 6,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 34,39</t>
+          <t>5,69; 34,38</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,31</t>
+          <t>1,02; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,75</t>
+          <t>2,64; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,87</t>
+          <t>2,0; 5,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,75</t>
+          <t>2,25; 5,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,91</t>
+          <t>2,75; 5,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,03</t>
+          <t>5,67; 9,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,04</t>
+          <t>5,25; 9,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,62</t>
+          <t>3,53; 6,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,19</t>
+          <t>2,19; 4,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,15</t>
+          <t>4,49; 6,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,28</t>
+          <t>3,92; 6,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,79</t>
+          <t>3,34; 5,62</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,11</t>
+          <t>0,91; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,11</t>
+          <t>1,21; 4,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,43</t>
+          <t>1,01; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,54</t>
+          <t>1,43; 5,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,95</t>
+          <t>1,69; 4,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,92</t>
+          <t>3,68; 7,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,48</t>
+          <t>3,55; 7,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,43</t>
+          <t>4,46; 7,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,8</t>
+          <t>1,74; 4,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,32</t>
+          <t>2,87; 5,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,79</t>
+          <t>2,58; 4,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,83</t>
+          <t>2,59; 5,84</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,02</t>
+          <t>1,32; 5,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,9</t>
+          <t>0,97; 3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,17</t>
+          <t>2,57; 6,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,82</t>
+          <t>0,84; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,48</t>
+          <t>3,07; 7,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,85</t>
+          <t>3,5; 7,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,81</t>
+          <t>3,16; 5,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,49</t>
+          <t>2,42; 5,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,85</t>
+          <t>1,65; 3,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,41</t>
+          <t>3,31; 6,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,95</t>
+          <t>2,26; 3,92</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,65</t>
+          <t>0,62; 4,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,46</t>
+          <t>2,02; 6,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,41</t>
+          <t>0,55; 3,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,3</t>
+          <t>0,95; 3,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,19</t>
+          <t>2,69; 7,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,73</t>
+          <t>2,51; 6,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,43</t>
+          <t>1,82; 5,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,58</t>
+          <t>0,95; 4,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,03</t>
+          <t>2,17; 5,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,13</t>
+          <t>2,83; 5,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,82</t>
+          <t>1,44; 3,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,52</t>
+          <t>1,12; 3,4</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,4</t>
+          <t>0,78; 5,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,55</t>
+          <t>1,76; 7,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,82</t>
+          <t>1,66; 5,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,23</t>
+          <t>1,12; 4,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,18</t>
+          <t>0,98; 4,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,18</t>
+          <t>1,99; 6,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,5</t>
+          <t>1,98; 6,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,11</t>
+          <t>1,8; 4,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,05</t>
+          <t>1,23; 4,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,75</t>
+          <t>2,43; 5,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,5</t>
+          <t>2,29; 5,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,67</t>
+          <t>1,78; 3,57</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,01</t>
+          <t>1,86; 2,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,12</t>
+          <t>2,78; 4,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,7</t>
+          <t>2,51; 3,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,14</t>
+          <t>2,42; 4,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,59</t>
+          <t>3,27; 4,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,35</t>
+          <t>4,74; 6,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,2</t>
+          <t>4,68; 6,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,66</t>
+          <t>4,21; 13,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,64</t>
+          <t>2,74; 3,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,02</t>
+          <t>4,02; 5,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,74; 4,77</t>
+          <t>3,78; 4,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,79</t>
+          <t>3,7; 8,08</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9813; 25591</t>
+          <t>10040; 25471</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11375; 28696</t>
+          <t>11163; 28148</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10500; 26998</t>
+          <t>9766; 27525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6470; 32955</t>
+          <t>7101; 35990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10653; 26329</t>
+          <t>11226; 25860</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18875; 39866</t>
+          <t>19198; 39258</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14372; 32702</t>
+          <t>13916; 32215</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4097; 22428</t>
+          <t>4659; 22149</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23862; 47757</t>
+          <t>24781; 46474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33549; 59157</t>
+          <t>34048; 60975</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27970; 52348</t>
+          <t>27578; 51943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14098; 48000</t>
+          <t>14327; 47460</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11286; 30437</t>
+          <t>10701; 29609</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18239; 40101</t>
+          <t>17553; 39245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13772; 31748</t>
+          <t>13458; 30707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13596; 40805</t>
+          <t>13342; 39112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17628; 38855</t>
+          <t>17097; 39132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27305; 50312</t>
+          <t>26575; 51873</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23896; 47095</t>
+          <t>24236; 46079</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30206; 259330</t>
+          <t>29764; 266916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31648; 59518</t>
+          <t>31951; 60253</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49834; 82421</t>
+          <t>51571; 83369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41916; 70576</t>
+          <t>42949; 72145</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52272; 321557</t>
+          <t>53209; 321489</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6583; 21090</t>
+          <t>6517; 19931</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16857; 39092</t>
+          <t>17974; 40953</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13211; 32574</t>
+          <t>13377; 34132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12473; 30817</t>
+          <t>12071; 30990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19126; 40765</t>
+          <t>18992; 39137</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41347; 70782</t>
+          <t>40002; 68271</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34071; 59772</t>
+          <t>34737; 61222</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19622; 35934</t>
+          <t>19176; 35586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29193; 55613</t>
+          <t>29109; 53351</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62905; 99158</t>
+          <t>62225; 96664</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52170; 83501</t>
+          <t>52128; 83915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36449; 62419</t>
+          <t>36055; 60678</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4267; 21356</t>
+          <t>4718; 19979</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7432; 25255</t>
+          <t>7444; 25879</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6910; 22160</t>
+          <t>6548; 21771</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11685; 49205</t>
+          <t>12696; 47958</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9481; 25543</t>
+          <t>8717; 25574</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23590; 48625</t>
+          <t>22586; 48310</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22863; 48574</t>
+          <t>23062; 48852</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31831; 52965</t>
+          <t>31794; 53277</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17840; 39371</t>
+          <t>18047; 41565</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35713; 65373</t>
+          <t>35269; 66117</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33023; 62065</t>
+          <t>33366; 61773</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45158; 93284</t>
+          <t>41488; 93418</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5189; 19413</t>
+          <t>5091; 19561</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4165; 16716</t>
+          <t>4175; 16014</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11190; 29467</t>
+          <t>12273; 30075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4929; 15816</t>
+          <t>4702; 15813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12317; 30232</t>
+          <t>12404; 30561</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8080; 23181</t>
+          <t>8081; 23200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16851; 39008</t>
+          <t>17386; 39516</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16880; 31676</t>
+          <t>17200; 30993</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20484; 43448</t>
+          <t>19108; 41778</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14627; 33775</t>
+          <t>14492; 33251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33138; 62530</t>
+          <t>32243; 60904</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24666; 43602</t>
+          <t>25002; 43362</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1810; 10684</t>
+          <t>1825; 12374</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6237; 22975</t>
+          <t>6209; 21258</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1850; 11406</t>
+          <t>1841; 10498</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3443; 12150</t>
+          <t>3498; 12320</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9379; 24667</t>
+          <t>9226; 24489</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8757; 23759</t>
+          <t>8847; 24180</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5945; 20520</t>
+          <t>6866; 20586</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6802; 27871</t>
+          <t>5808; 27941</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14359; 31966</t>
+          <t>13781; 31873</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18068; 40494</t>
+          <t>18695; 39074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10027; 27188</t>
+          <t>10235; 27841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11293; 34326</t>
+          <t>10936; 33163</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1707; 11334</t>
+          <t>1636; 11419</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4313; 18804</t>
+          <t>4375; 18444</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4102; 14953</t>
+          <t>4273; 15139</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3057; 11941</t>
+          <t>3155; 11495</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3370; 17299</t>
+          <t>3264; 16301</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7609; 23822</t>
+          <t>7675; 23887</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9062; 26003</t>
+          <t>7935; 26327</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7746; 17455</t>
+          <t>7648; 17552</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6471; 22027</t>
+          <t>6662; 23387</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15126; 36511</t>
+          <t>15447; 36798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15638; 36121</t>
+          <t>15034; 35223</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12652; 25970</t>
+          <t>12556; 25201</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>61545; 98468</t>
+          <t>61076; 96429</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>97114; 140864</t>
+          <t>94908; 139426</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85287; 125454</t>
+          <t>85196; 126112</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>84475; 143314</t>
+          <t>83532; 141710</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>110742; 154949</t>
+          <t>110391; 157218</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>169425; 224957</t>
+          <t>167870; 224586</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>163880; 219774</t>
+          <t>165895; 218225</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>152869; 463207</t>
+          <t>153989; 503983</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>180513; 242450</t>
+          <t>182254; 242954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>274781; 349313</t>
+          <t>279694; 352409</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>259786; 330773</t>
+          <t>262087; 332000</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>261143; 625379</t>
+          <t>263416; 574729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A08-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,16</t>
+          <t>2,09; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,21</t>
+          <t>2,53; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,56</t>
+          <t>2,57; 6,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,0</t>
+          <t>1,35; 6,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,53</t>
+          <t>2,42; 5,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,14</t>
+          <t>4,3; 9,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,14</t>
+          <t>3,64; 8,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,07</t>
+          <t>1,76; 7,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,83</t>
+          <t>2,52; 4,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,91</t>
+          <t>3,75; 6,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,37</t>
+          <t>3,39; 6,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,65</t>
+          <t>2,11; 5,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,03</t>
+          <t>1,43; 3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,72</t>
+          <t>2,53; 5,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,2</t>
+          <t>2,25; 5,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,23</t>
+          <t>2,9; 7,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,26</t>
+          <t>2,68; 6,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,51</t>
+          <t>4,46; 8,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,18</t>
+          <t>4,5; 8,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 52,18</t>
+          <t>4,6; 9,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,43</t>
+          <t>2,36; 4,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,44</t>
+          <t>3,9; 6,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,25</t>
+          <t>3,67; 6,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 34,38</t>
+          <t>4,42; 7,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,13</t>
+          <t>1,04; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,02</t>
+          <t>2,68; 6,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,1</t>
+          <t>1,84; 4,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,78</t>
+          <t>2,37; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,67</t>
+          <t>2,8; 5,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,67</t>
+          <t>5,63; 9,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,26</t>
+          <t>5,22; 8,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,56</t>
+          <t>3,6; 6,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,02</t>
+          <t>2,17; 3,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,97</t>
+          <t>4,59; 7,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,31</t>
+          <t>3,9; 6,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,62</t>
+          <t>3,28; 5,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,85</t>
+          <t>0,9; 3,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,21</t>
+          <t>1,19; 4,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,37</t>
+          <t>1,04; 3,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,4</t>
+          <t>3,23; 6,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,96</t>
+          <t>1,71; 4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,87</t>
+          <t>3,93; 7,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,53</t>
+          <t>3,6; 7,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,47</t>
+          <t>5,15; 8,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,02</t>
+          <t>1,65; 3,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,38</t>
+          <t>2,92; 5,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,77</t>
+          <t>2,53; 4,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,84</t>
+          <t>4,68; 6,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,06</t>
+          <t>1,19; 5,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,74</t>
+          <t>0,97; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,29</t>
+          <t>2,51; 6,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,82</t>
+          <t>0,89; 3,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,56</t>
+          <t>3,06; 7,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,18</t>
+          <t>1,84; 5,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,95</t>
+          <t>3,56; 8,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,69</t>
+          <t>3,12; 5,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,28</t>
+          <t>2,61; 5,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,8</t>
+          <t>1,64; 3,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,25</t>
+          <t>3,33; 6,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,92</t>
+          <t>2,25; 3,94</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,23</t>
+          <t>0,49; 3,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,91</t>
+          <t>2,26; 7,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,14</t>
+          <t>0,56; 3,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,35</t>
+          <t>0,91; 3,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,14</t>
+          <t>2,84; 7,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,85</t>
+          <t>2,44; 6,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,45</t>
+          <t>1,69; 5,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,59</t>
+          <t>3,04; 5,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,02</t>
+          <t>2,06; 4,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,91</t>
+          <t>2,79; 5,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,91</t>
+          <t>1,42; 3,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,4</t>
+          <t>2,27; 4,0</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,44</t>
+          <t>0,82; 5,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,41</t>
+          <t>1,68; 7,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,89</t>
+          <t>1,59; 5,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,07</t>
+          <t>1,17; 4,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,88</t>
+          <t>0,98; 4,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,19</t>
+          <t>2,23; 6,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,58</t>
+          <t>2,27; 6,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,14</t>
+          <t>1,84; 4,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,3</t>
+          <t>1,07; 3,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,8</t>
+          <t>2,52; 5,55</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,36</t>
+          <t>2,45; 5,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,57</t>
+          <t>1,85; 3,76</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,94</t>
+          <t>1,89; 2,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,08</t>
+          <t>2,78; 4,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,72</t>
+          <t>2,57; 3,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,1</t>
+          <t>2,82; 4,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,65</t>
+          <t>3,32; 4,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,34</t>
+          <t>4,72; 6,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,16</t>
+          <t>4,62; 6,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,78</t>
+          <t>4,36; 5,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,65</t>
+          <t>2,73; 3,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,06</t>
+          <t>3,99; 5,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 4,78</t>
+          <t>3,77; 4,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,08</t>
+          <t>3,77; 4,68</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26420</t>
+          <t>28280</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10040; 25471</t>
+          <t>10329; 26150</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11163; 28148</t>
+          <t>11461; 28297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9766; 27525</t>
+          <t>10785; 26668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7101; 35990</t>
+          <t>5522; 27398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11226; 25860</t>
+          <t>11296; 27592</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19198; 39258</t>
+          <t>18444; 39623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13916; 32215</t>
+          <t>14407; 32581</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4659; 22149</t>
+          <t>6392; 27953</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24781; 46474</t>
+          <t>24235; 46855</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34048; 60975</t>
+          <t>33085; 59993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27578; 51943</t>
+          <t>27661; 52052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14327; 47460</t>
+          <t>16233; 45976</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23947</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>99044</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>122991</t>
+          <t>57648</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10701; 29609</t>
+          <t>10554; 28972</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17553; 39245</t>
+          <t>17335; 38679</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13458; 30707</t>
+          <t>13279; 30771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13342; 39112</t>
+          <t>13836; 37812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17097; 39132</t>
+          <t>16738; 37962</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26575; 51873</t>
+          <t>27192; 51086</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24236; 46079</t>
+          <t>25334; 47999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29764; 266916</t>
+          <t>23035; 48603</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31951; 60253</t>
+          <t>32056; 60695</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51571; 83369</t>
+          <t>50482; 83478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42949; 72145</t>
+          <t>42400; 71880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53209; 321489</t>
+          <t>43233; 78004</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>23320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>53973</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6517; 19931</t>
+          <t>6645; 21520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17974; 40953</t>
+          <t>18221; 41691</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13377; 34132</t>
+          <t>12278; 32004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12071; 30990</t>
+          <t>14705; 35464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18992; 39137</t>
+          <t>19342; 40838</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40002; 68271</t>
+          <t>39754; 68137</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34737; 61222</t>
+          <t>34508; 59180</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19176; 35586</t>
+          <t>22408; 41180</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29109; 53351</t>
+          <t>28856; 52830</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62225; 96664</t>
+          <t>63571; 98726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52128; 83915</t>
+          <t>51898; 86098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36055; 60678</t>
+          <t>40756; 68479</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>47507</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71832</t>
+          <t>81055</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4718; 19979</t>
+          <t>4696; 20483</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7444; 25879</t>
+          <t>7308; 27304</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6548; 21771</t>
+          <t>6748; 23497</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12696; 47958</t>
+          <t>22640; 46901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8717; 25574</t>
+          <t>8816; 24490</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22586; 48310</t>
+          <t>24160; 48398</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23062; 48852</t>
+          <t>23364; 49320</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31794; 53277</t>
+          <t>37964; 59628</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18047; 41565</t>
+          <t>17083; 38880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35269; 66117</t>
+          <t>35861; 64611</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33366; 61773</t>
+          <t>32768; 61177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41488; 93418</t>
+          <t>67343; 100493</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32865</t>
+          <t>36973</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5091; 19561</t>
+          <t>4617; 20310</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4175; 16014</t>
+          <t>4137; 15286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12273; 30075</t>
+          <t>12001; 30438</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4702; 15813</t>
+          <t>5399; 19041</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12404; 30561</t>
+          <t>12362; 31435</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8081; 23200</t>
+          <t>8228; 23450</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17386; 39516</t>
+          <t>17702; 40727</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17200; 30993</t>
+          <t>18932; 35925</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19108; 41778</t>
+          <t>20625; 43629</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14492; 33251</t>
+          <t>14337; 32553</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32243; 60904</t>
+          <t>32417; 60494</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25002; 43362</t>
+          <t>27400; 47867</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>25940</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1825; 12374</t>
+          <t>1426; 11174</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6209; 21258</t>
+          <t>6954; 21731</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1841; 10498</t>
+          <t>1876; 10558</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3498; 12320</t>
+          <t>3704; 13300</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9226; 24489</t>
+          <t>9756; 26015</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8847; 24180</t>
+          <t>8627; 23801</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6866; 20586</t>
+          <t>6392; 21406</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5808; 27941</t>
+          <t>13369; 25641</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13781; 31873</t>
+          <t>13114; 30878</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18695; 39074</t>
+          <t>18421; 39345</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10235; 27841</t>
+          <t>10129; 27108</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10936; 33163</t>
+          <t>19214; 33885</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>20597</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1636; 11419</t>
+          <t>1711; 10603</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4375; 18444</t>
+          <t>4185; 18178</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4273; 15139</t>
+          <t>4089; 14818</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3155; 11495</t>
+          <t>3637; 12830</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3264; 16301</t>
+          <t>3269; 15734</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7675; 23887</t>
+          <t>8608; 23219</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7935; 26327</t>
+          <t>9102; 26208</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7648; 17552</t>
+          <t>8513; 19742</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6662; 23387</t>
+          <t>5796; 21718</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15447; 36798</t>
+          <t>15976; 35209</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15034; 35223</t>
+          <t>16075; 36782</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12556; 25201</t>
+          <t>14308; 29050</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>304467</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>61076; 96429</t>
+          <t>61806; 97361</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>94908; 139426</t>
+          <t>95064; 139924</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85196; 126112</t>
+          <t>87399; 125072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>83532; 141710</t>
+          <t>99673; 146731</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>110391; 157218</t>
+          <t>112128; 156802</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>167870; 224586</t>
+          <t>167255; 223801</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>165895; 218225</t>
+          <t>163853; 221970</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>153989; 503983</t>
+          <t>162551; 211185</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>182254; 242954</t>
+          <t>181916; 238183</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>279694; 352409</t>
+          <t>278194; 348033</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>262087; 332000</t>
+          <t>261314; 327835</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>263416; 574729</t>
+          <t>273514; 339927</t>
         </is>
       </c>
     </row>
